--- a/data/trans_dic/P79$alquiler_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79$alquiler_2023-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,07</t>
+          <t>0,2; 2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,71</t>
+          <t>0,29; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,52</t>
+          <t>0,39; 1,74</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,27</t>
+          <t>0,82; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,56</t>
+          <t>1,0; 4,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,44</t>
+          <t>1,16; 3,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,66</t>
+          <t>0,68; 5,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,81</t>
+          <t>1,58; 6,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,17</t>
+          <t>1,54; 5,05</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,19</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,76</t>
+          <t>0,1; 0,87</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,72</t>
+          <t>0,62; 3,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,08</t>
+          <t>1,35; 5,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,66</t>
+          <t>1,22; 3,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,81</t>
+          <t>0,32; 1,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,99</t>
+          <t>1,33; 3,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,64</t>
+          <t>1,07; 2,51</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,48</t>
+          <t>3,34; 6,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,48</t>
+          <t>2,85; 5,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,43</t>
+          <t>3,31; 5,64</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,95</t>
+          <t>1,41; 2,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,49</t>
+          <t>1,88; 2,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,12</t>
+          <t>1,78; 2,54</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 23602</t>
+          <t>0; 15564</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 24452</t>
+          <t>0; 14885</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8817</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>936; 10455</t>
+          <t>1059; 11637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1039; 8587</t>
+          <t>1555; 12172</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3159; 15281</t>
+          <t>4074; 18315</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13776</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1764; 13324</t>
+          <t>2558; 14661</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3261; 15306</t>
+          <t>3442; 14420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6706; 22314</t>
+          <t>7580; 23108</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>19405</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1298; 13888</t>
+          <t>2415; 18151</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5300; 22204</t>
+          <t>6227; 25386</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8326; 28398</t>
+          <t>11512; 37752</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1367</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13; 3018</t>
+          <t>441; 4076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181; 3266</t>
+          <t>443; 3717</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>11129</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>985; 7186</t>
+          <t>1654; 10514</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2149; 10365</t>
+          <t>3524; 13222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4122; 13807</t>
+          <t>6399; 18688</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>23166</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1406; 10687</t>
+          <t>2182; 13361</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3482; 16265</t>
+          <t>9732; 27115</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7802; 23071</t>
+          <t>15113; 35502</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>25887</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51373</t>
+          <t>68957</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10275; 40972</t>
+          <t>26103; 52709</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17583; 37839</t>
+          <t>22815; 44797</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30264; 71198</t>
+          <t>52412; 89261</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>34323; 65621</t>
+          <t>48295; 85539</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48871; 87640</t>
+          <t>67680; 105514</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90124; 146012</t>
+          <t>125300; 178156</t>
         </is>
       </c>
     </row>
